--- a/Iren Model.xlsx
+++ b/Iren Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C23D2C-A326-4722-AF64-6860649D0538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285E924D-8763-49F1-AEEC-8B565B0F9C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="16680" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26268" yWindow="540" windowWidth="23016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF Model" sheetId="2" r:id="rId1"/>
@@ -818,13 +818,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -833,9 +836,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2210,7 +2210,7 @@
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B36" s="94" t="s">
+      <c r="B36" s="96" t="s">
         <v>73</v>
       </c>
       <c r="C36" s="81">
@@ -2267,7 +2267,7 @@
       <c r="P36" s="52"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B37" s="94"/>
+      <c r="B37" s="96"/>
       <c r="C37" s="81">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="P37" s="52"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B38" s="94"/>
+      <c r="B38" s="96"/>
       <c r="C38" s="81">
         <v>0.02</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="P38" s="52"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B39" s="94"/>
+      <c r="B39" s="96"/>
       <c r="C39" s="81">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -2432,7 +2432,7 @@
       <c r="P39" s="52"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B40" s="94"/>
+      <c r="B40" s="96"/>
       <c r="C40" s="81">
         <v>0.03</v>
       </c>
@@ -2487,7 +2487,7 @@
       <c r="P40" s="52"/>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B41" s="94"/>
+      <c r="B41" s="96"/>
       <c r="C41" s="81">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="P41" s="52"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B42" s="94"/>
+      <c r="B42" s="96"/>
       <c r="C42" s="81">
         <v>0.04</v>
       </c>
@@ -2597,7 +2597,7 @@
       <c r="P42" s="52"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B43" s="94"/>
+      <c r="B43" s="96"/>
       <c r="C43" s="81">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -2652,7 +2652,7 @@
       <c r="P43" s="52"/>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B44" s="94"/>
+      <c r="B44" s="96"/>
       <c r="C44" s="81">
         <v>0.05</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B48" s="94" t="s">
+      <c r="B48" s="96" t="s">
         <v>75</v>
       </c>
       <c r="C48" s="81">
@@ -2807,7 +2807,7 @@
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B49" s="94"/>
+      <c r="B49" s="96"/>
       <c r="C49" s="81">
         <v>0.09</v>
       </c>
@@ -2861,7 +2861,7 @@
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B50" s="94"/>
+      <c r="B50" s="96"/>
       <c r="C50" s="81">
         <v>0.1</v>
       </c>
@@ -2915,7 +2915,7 @@
       </c>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B51" s="94"/>
+      <c r="B51" s="96"/>
       <c r="C51" s="81">
         <v>0.11</v>
       </c>
@@ -2969,7 +2969,7 @@
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B52" s="94"/>
+      <c r="B52" s="96"/>
       <c r="C52" s="81">
         <v>0.12</v>
       </c>
@@ -3023,7 +3023,7 @@
       </c>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B53" s="94"/>
+      <c r="B53" s="96"/>
       <c r="C53" s="81">
         <v>0.13</v>
       </c>
@@ -3077,7 +3077,7 @@
       </c>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B54" s="94"/>
+      <c r="B54" s="96"/>
       <c r="C54" s="81">
         <v>0.14000000000000001</v>
       </c>
@@ -3131,7 +3131,7 @@
       </c>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B55" s="94"/>
+      <c r="B55" s="96"/>
       <c r="C55" s="81">
         <v>0.15</v>
       </c>
@@ -3185,7 +3185,7 @@
       </c>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B56" s="94"/>
+      <c r="B56" s="96"/>
       <c r="C56" s="81">
         <v>0.16</v>
       </c>
@@ -3239,7 +3239,7 @@
       </c>
     </row>
     <row r="57" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="94"/>
+      <c r="B57" s="96"/>
       <c r="C57" s="81">
         <v>0.17</v>
       </c>
@@ -3293,7 +3293,7 @@
       </c>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B58" s="94"/>
+      <c r="B58" s="96"/>
       <c r="C58" s="81">
         <v>0.18</v>
       </c>
@@ -3347,7 +3347,7 @@
       </c>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B59" s="94"/>
+      <c r="B59" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3411,22 +3411,22 @@
         <v>2031</v>
       </c>
       <c r="K4" s="2"/>
-      <c r="L4" s="93" t="s">
+      <c r="L4" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93" t="s">
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="P4" s="93"/>
-      <c r="Q4" s="93"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="98"/>
       <c r="R4" s="2"/>
-      <c r="S4" s="93" t="s">
+      <c r="S4" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="93"/>
-      <c r="U4" s="93"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -3451,11 +3451,11 @@
         <v>1455</v>
       </c>
       <c r="K5" s="1"/>
-      <c r="L5" s="95" t="s">
+      <c r="L5" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
       <c r="O5" t="s">
         <v>44</v>
       </c>
@@ -3463,11 +3463,11 @@
         <f>E15*22.55</f>
         <v>43747</v>
       </c>
-      <c r="S5" s="95" t="s">
+      <c r="S5" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="T5" s="95"/>
-      <c r="U5" s="95"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="97"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
@@ -3504,11 +3504,11 @@
         <f>4160*22.55</f>
         <v>93808</v>
       </c>
-      <c r="S6" s="95" t="s">
+      <c r="S6" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="T6" s="95"/>
-      <c r="U6" s="95"/>
+      <c r="T6" s="97"/>
+      <c r="U6" s="97"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
@@ -3546,11 +3546,11 @@
         <f>E24*22.55</f>
         <v>81180</v>
       </c>
-      <c r="S7" s="95" t="s">
+      <c r="S7" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="T7" s="95"/>
-      <c r="U7" s="95"/>
+      <c r="T7" s="97"/>
+      <c r="U7" s="97"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
@@ -3580,9 +3580,9 @@
         <f t="shared" si="2"/>
         <v>0.85</v>
       </c>
-      <c r="L8" s="95"/>
-      <c r="M8" s="95"/>
-      <c r="N8" s="95"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="97"/>
       <c r="O8" t="s">
         <v>47</v>
       </c>
@@ -3590,7 +3590,7 @@
         <f>SUM(Q5:Q7)</f>
         <v>218735</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="24">
         <f>Q7/Q8</f>
         <v>0.37113402061855671</v>
       </c>
@@ -3631,11 +3631,11 @@
         <f>4640/5*0.75</f>
         <v>696</v>
       </c>
-      <c r="L10" s="95" t="s">
+      <c r="L10" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="95"/>
-      <c r="N10" s="95"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="97"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
@@ -3778,11 +3778,11 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="L16" s="95" t="s">
+      <c r="L16" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="M16" s="95"/>
-      <c r="N16" s="95"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="97"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
@@ -3800,11 +3800,11 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="L17" s="95" t="s">
+      <c r="L17" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="M17" s="95"/>
-      <c r="N17" s="95"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
@@ -3831,11 +3831,11 @@
         <f t="shared" si="8"/>
         <v>-100</v>
       </c>
-      <c r="L18" s="95" t="s">
+      <c r="L18" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="95"/>
-      <c r="N18" s="95"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
@@ -3952,11 +3952,11 @@
         <f>$E$24*-0.06*0.5</f>
         <v>-108</v>
       </c>
-      <c r="L25" s="95" t="s">
+      <c r="L25" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="M25" s="95"/>
-      <c r="N25" s="95"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
@@ -4040,11 +4040,11 @@
         <f t="shared" si="11"/>
         <v>1876.1858083275031</v>
       </c>
-      <c r="L30" s="95" t="s">
+      <c r="L30" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="M30" s="95"/>
-      <c r="N30" s="95"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
@@ -4075,11 +4075,11 @@
         <f t="shared" si="12"/>
         <v>-111.92506608226513</v>
       </c>
-      <c r="L31" s="95" t="s">
+      <c r="L31" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="M31" s="95"/>
-      <c r="N31" s="95"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
@@ -4099,9 +4099,9 @@
       <c r="J33" s="55">
         <v>77000</v>
       </c>
-      <c r="L33" s="95"/>
-      <c r="M33" s="95"/>
-      <c r="N33" s="95"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="14" t="s">
@@ -4122,9 +4122,9 @@
         <f>9700000000/(J33*43800)</f>
         <v>2.8761193144754786</v>
       </c>
-      <c r="L34" s="95"/>
-      <c r="M34" s="95"/>
-      <c r="N34" s="95"/>
+      <c r="L34" s="97"/>
+      <c r="M34" s="97"/>
+      <c r="N34" s="97"/>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
@@ -4171,13 +4171,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L17:N17"/>
     <mergeCell ref="S4:U4"/>
     <mergeCell ref="S5:U5"/>
     <mergeCell ref="S6:U6"/>
@@ -4188,6 +4181,13 @@
     <mergeCell ref="L8:N8"/>
     <mergeCell ref="L10:N10"/>
     <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L17:N17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4308,40 +4308,40 @@
       <c r="Z4" s="2">
         <v>2047</v>
       </c>
-      <c r="AA4" s="93" t="s">
+      <c r="AA4" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="AB4" s="93"/>
-      <c r="AC4" s="93"/>
-      <c r="AD4" s="93" t="s">
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="98"/>
+      <c r="AD4" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="AE4" s="93"/>
-      <c r="AF4" s="93"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
       <c r="AG4" s="2"/>
-      <c r="AH4" s="93" t="s">
+      <c r="AH4" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="AI4" s="93"/>
-      <c r="AJ4" s="93"/>
-      <c r="AK4" s="93" t="s">
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="98"/>
+      <c r="AK4" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="AL4" s="93"/>
-      <c r="AM4" s="93"/>
-      <c r="AN4" s="93"/>
-      <c r="AO4" s="93"/>
-      <c r="AP4" s="93"/>
-      <c r="AQ4" s="93"/>
-      <c r="AR4" s="93"/>
-      <c r="AS4" s="93"/>
-      <c r="AT4" s="93"/>
-      <c r="AU4" s="93"/>
-      <c r="AV4" s="93"/>
-      <c r="AW4" s="93"/>
-      <c r="AX4" s="93"/>
-      <c r="AY4" s="93"/>
-      <c r="AZ4" s="93"/>
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="98"/>
+      <c r="AR4" s="98"/>
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="98"/>
+      <c r="AY4" s="98"/>
+      <c r="AZ4" s="98"/>
     </row>
     <row r="5" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -4410,11 +4410,11 @@
       <c r="Y5" s="40">
         <v>1940</v>
       </c>
-      <c r="AA5" s="95" t="s">
+      <c r="AA5" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="AB5" s="95"/>
-      <c r="AC5" s="95"/>
+      <c r="AB5" s="97"/>
+      <c r="AC5" s="97"/>
       <c r="AD5" t="s">
         <v>44</v>
       </c>
@@ -4422,27 +4422,27 @@
         <f>(E16*4)*22.55</f>
         <v>174988</v>
       </c>
-      <c r="AH5" s="95" t="s">
+      <c r="AH5" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="AI5" s="95"/>
-      <c r="AJ5" s="95"/>
-      <c r="AM5" s="96" t="s">
+      <c r="AI5" s="97"/>
+      <c r="AJ5" s="97"/>
+      <c r="AM5" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="AN5" s="96"/>
-      <c r="AO5" s="96"/>
-      <c r="AP5" s="96"/>
-      <c r="AQ5" s="96"/>
-      <c r="AR5" s="96"/>
-      <c r="AS5" s="96"/>
-      <c r="AT5" s="96"/>
-      <c r="AU5" s="96"/>
-      <c r="AV5" s="96"/>
-      <c r="AW5" s="96"/>
-      <c r="AX5" s="96"/>
-      <c r="AY5" s="96"/>
-      <c r="AZ5" s="96"/>
+      <c r="AN5" s="99"/>
+      <c r="AO5" s="99"/>
+      <c r="AP5" s="99"/>
+      <c r="AQ5" s="99"/>
+      <c r="AR5" s="99"/>
+      <c r="AS5" s="99"/>
+      <c r="AT5" s="99"/>
+      <c r="AU5" s="99"/>
+      <c r="AV5" s="99"/>
+      <c r="AW5" s="99"/>
+      <c r="AX5" s="99"/>
+      <c r="AY5" s="99"/>
+      <c r="AZ5" s="99"/>
     </row>
     <row r="6" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
@@ -4539,11 +4539,11 @@
         <f>(4160)+((2200)*3)*22.55</f>
         <v>152990</v>
       </c>
-      <c r="AH6" s="95" t="s">
+      <c r="AH6" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="AI6" s="95"/>
-      <c r="AJ6" s="95"/>
+      <c r="AI6" s="97"/>
+      <c r="AJ6" s="97"/>
       <c r="AM6" s="54">
         <v>1</v>
       </c>
@@ -4683,12 +4683,12 @@
         <f>(E25*4)*22.55</f>
         <v>324720</v>
       </c>
-      <c r="AH7" s="95" t="s">
+      <c r="AH7" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="AI7" s="95"/>
-      <c r="AJ7" s="95"/>
-      <c r="AK7" s="97" t="s">
+      <c r="AI7" s="97"/>
+      <c r="AJ7" s="97"/>
+      <c r="AK7" s="100" t="s">
         <v>73</v>
       </c>
       <c r="AL7" s="60">
@@ -4839,9 +4839,9 @@
         <f t="shared" si="4"/>
         <v>0.85</v>
       </c>
-      <c r="AA8" s="95"/>
-      <c r="AB8" s="95"/>
-      <c r="AC8" s="95"/>
+      <c r="AA8" s="97"/>
+      <c r="AB8" s="97"/>
+      <c r="AC8" s="97"/>
       <c r="AD8" t="s">
         <v>47</v>
       </c>
@@ -4849,7 +4849,7 @@
         <f>SUM(AF5:AF7)</f>
         <v>652698</v>
       </c>
-      <c r="AK8" s="97"/>
+      <c r="AK8" s="100"/>
       <c r="AL8" s="60">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -4921,7 +4921,7 @@
       <c r="P9" s="37"/>
       <c r="U9" s="37"/>
       <c r="Y9" s="43"/>
-      <c r="AK9" s="97"/>
+      <c r="AK9" s="100"/>
       <c r="AL9" s="60">
         <v>0.02</v>
       </c>
@@ -5070,11 +5070,11 @@
         <f t="shared" si="5"/>
         <v>928</v>
       </c>
-      <c r="AA10" s="95" t="s">
+      <c r="AA10" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="AB10" s="95"/>
-      <c r="AC10" s="95"/>
+      <c r="AB10" s="97"/>
+      <c r="AC10" s="97"/>
       <c r="AD10" t="s">
         <v>53</v>
       </c>
@@ -5082,7 +5082,7 @@
         <f>SUM(E23:Y23)*22.5</f>
         <v>165830.0625</v>
       </c>
-      <c r="AK10" s="97"/>
+      <c r="AK10" s="100"/>
       <c r="AL10" s="60">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -5238,7 +5238,7 @@
         <f>SUM(E29:Y29)*22.5</f>
         <v>84145.612500000047</v>
       </c>
-      <c r="AK11" s="97"/>
+      <c r="AK11" s="100"/>
       <c r="AL11" s="60">
         <v>0.03</v>
       </c>
@@ -5387,7 +5387,7 @@
         <f t="shared" si="7"/>
         <v>608.5</v>
       </c>
-      <c r="AK12" s="97"/>
+      <c r="AK12" s="100"/>
       <c r="AL12" s="60">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -5536,7 +5536,7 @@
         <f t="shared" si="8"/>
         <v>103.44500000000001</v>
       </c>
-      <c r="AK13" s="97"/>
+      <c r="AK13" s="100"/>
       <c r="AL13" s="60">
         <v>0.04</v>
       </c>
@@ -5615,7 +5615,7 @@
         <f>E34*22.5</f>
         <v>-13103.971175407411</v>
       </c>
-      <c r="AK14" s="97"/>
+      <c r="AK14" s="100"/>
       <c r="AL14" s="60">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5771,7 +5771,7 @@
         <f>E35*22.5</f>
         <v>16460.011887084675</v>
       </c>
-      <c r="AK15" s="97"/>
+      <c r="AK15" s="100"/>
       <c r="AL15" s="60">
         <v>0.05</v>
       </c>
@@ -5940,11 +5940,11 @@
       <c r="P17" s="37"/>
       <c r="U17" s="37"/>
       <c r="Y17" s="43"/>
-      <c r="AA17" s="95" t="s">
+      <c r="AA17" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="95"/>
+      <c r="AB17" s="97"/>
+      <c r="AC17" s="97"/>
       <c r="AD17" t="s">
         <v>72</v>
       </c>
@@ -5982,11 +5982,11 @@
         <v>-5800</v>
       </c>
       <c r="Y18" s="43"/>
-      <c r="AA18" s="95" t="s">
+      <c r="AA18" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="AB18" s="95"/>
-      <c r="AC18" s="95"/>
+      <c r="AB18" s="97"/>
+      <c r="AC18" s="97"/>
     </row>
     <row r="19" spans="2:52" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
@@ -6073,33 +6073,33 @@
         <f t="shared" si="14"/>
         <v>-100</v>
       </c>
-      <c r="AA19" s="95" t="s">
+      <c r="AA19" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="AB19" s="95"/>
-      <c r="AC19" s="95"/>
+      <c r="AB19" s="97"/>
+      <c r="AC19" s="97"/>
       <c r="AD19" t="s">
         <v>57</v>
       </c>
       <c r="AF19">
         <v>46.15</v>
       </c>
-      <c r="AM19" s="96" t="s">
+      <c r="AM19" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="AN19" s="96"/>
-      <c r="AO19" s="96"/>
-      <c r="AP19" s="96"/>
-      <c r="AQ19" s="96"/>
-      <c r="AR19" s="96"/>
-      <c r="AS19" s="96"/>
-      <c r="AT19" s="96"/>
-      <c r="AU19" s="96"/>
-      <c r="AV19" s="96"/>
-      <c r="AW19" s="96"/>
-      <c r="AX19" s="96"/>
-      <c r="AY19" s="96"/>
-      <c r="AZ19" s="96"/>
+      <c r="AN19" s="99"/>
+      <c r="AO19" s="99"/>
+      <c r="AP19" s="99"/>
+      <c r="AQ19" s="99"/>
+      <c r="AR19" s="99"/>
+      <c r="AS19" s="99"/>
+      <c r="AT19" s="99"/>
+      <c r="AU19" s="99"/>
+      <c r="AV19" s="99"/>
+      <c r="AW19" s="99"/>
+      <c r="AX19" s="99"/>
+      <c r="AY19" s="99"/>
+      <c r="AZ19" s="99"/>
     </row>
     <row r="20" spans="2:52" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
@@ -6136,12 +6136,12 @@
       <c r="AF20">
         <v>331.44</v>
       </c>
-      <c r="AH20" s="95" t="s">
+      <c r="AH20" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="AI20" s="95"/>
-      <c r="AJ20" s="95"/>
-      <c r="AK20" s="94" t="s">
+      <c r="AI20" s="97"/>
+      <c r="AJ20" s="97"/>
+      <c r="AK20" s="96" t="s">
         <v>75</v>
       </c>
       <c r="AM20" s="54">
@@ -6205,7 +6205,7 @@
         <f>AF19*AF20</f>
         <v>15295.956</v>
       </c>
-      <c r="AK21" s="94"/>
+      <c r="AK21" s="96"/>
       <c r="AL21" s="63">
         <v>0.08</v>
       </c>
@@ -6277,7 +6277,7 @@
       <c r="P22" s="37"/>
       <c r="U22" s="37"/>
       <c r="Y22" s="43"/>
-      <c r="AK22" s="94"/>
+      <c r="AK22" s="96"/>
       <c r="AL22" s="63">
         <v>0.09</v>
       </c>
@@ -6436,7 +6436,7 @@
         <f>AF6</f>
         <v>152990</v>
       </c>
-      <c r="AK23" s="94"/>
+      <c r="AK23" s="96"/>
       <c r="AL23" s="63">
         <v>0.1</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="AF24" s="54">
         <v>3</v>
       </c>
-      <c r="AK24" s="94"/>
+      <c r="AK24" s="96"/>
       <c r="AL24" s="63">
         <v>0.11</v>
       </c>
@@ -6598,12 +6598,12 @@
         <f>AF20*AF24</f>
         <v>994.31999999999994</v>
       </c>
-      <c r="AH25" s="95" t="s">
+      <c r="AH25" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="AI25" s="95"/>
-      <c r="AJ25" s="95"/>
-      <c r="AK25" s="94"/>
+      <c r="AI25" s="97"/>
+      <c r="AJ25" s="97"/>
+      <c r="AK25" s="96"/>
       <c r="AL25" s="63">
         <v>0.12</v>
       </c>
@@ -6752,12 +6752,12 @@
         <f t="shared" si="18"/>
         <v>-179.28</v>
       </c>
-      <c r="AA26" s="95" t="s">
+      <c r="AA26" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="AB26" s="95"/>
-      <c r="AC26" s="95"/>
-      <c r="AK26" s="94"/>
+      <c r="AB26" s="97"/>
+      <c r="AC26" s="97"/>
+      <c r="AK26" s="96"/>
       <c r="AL26" s="63">
         <v>0.13</v>
       </c>
@@ -6853,7 +6853,7 @@
         <f>AF17/AF25</f>
         <v>35.302413832981102</v>
       </c>
-      <c r="AK27" s="94"/>
+      <c r="AK27" s="96"/>
       <c r="AL27" s="63">
         <v>0.14000000000000001</v>
       </c>
@@ -6931,7 +6931,7 @@
       <c r="AF28" s="52">
         <v>46.15</v>
       </c>
-      <c r="AK28" s="94"/>
+      <c r="AK28" s="96"/>
       <c r="AL28" s="63">
         <v>0.15</v>
       </c>
@@ -7093,7 +7093,7 @@
         <f>AF27/AF28-1</f>
         <v>-0.23505062117050701</v>
       </c>
-      <c r="AK29" s="94"/>
+      <c r="AK29" s="96"/>
       <c r="AL29" s="63">
         <v>0.16</v>
       </c>
@@ -7159,7 +7159,7 @@
       <c r="P30" s="51"/>
       <c r="U30" s="51"/>
       <c r="Y30" s="51"/>
-      <c r="AK30" s="94"/>
+      <c r="AK30" s="96"/>
       <c r="AL30" s="63">
         <v>0.17</v>
       </c>
@@ -7309,12 +7309,12 @@
         <f t="shared" si="26"/>
         <v>191.88464144543519</v>
       </c>
-      <c r="AA31" s="95" t="s">
+      <c r="AA31" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="AB31" s="95"/>
-      <c r="AC31" s="95"/>
-      <c r="AK31" s="94"/>
+      <c r="AB31" s="97"/>
+      <c r="AC31" s="97"/>
+      <c r="AK31" s="96"/>
       <c r="AL31" s="63">
         <v>0.18</v>
       </c>
@@ -7468,11 +7468,11 @@
         <f>$Z$29/((1+$L$2)^($Z$4-YEAR($C$2)+0.5))</f>
         <v>18641.884235325091</v>
       </c>
-      <c r="AA32" s="95" t="s">
+      <c r="AA32" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="AB32" s="95"/>
-      <c r="AC32" s="95"/>
+      <c r="AB32" s="97"/>
+      <c r="AC32" s="97"/>
       <c r="AD32" t="s">
         <v>76</v>
       </c>
@@ -7480,11 +7480,11 @@
         <f>AF20/21</f>
         <v>15.782857142857143</v>
       </c>
-      <c r="AH32" s="95" t="s">
+      <c r="AH32" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="AI32" s="95"/>
-      <c r="AJ32" s="95"/>
+      <c r="AI32" s="97"/>
+      <c r="AJ32" s="97"/>
     </row>
     <row r="33" spans="2:36" x14ac:dyDescent="0.3">
       <c r="AD33" t="s">
@@ -7494,11 +7494,11 @@
         <f>AF6/AF21</f>
         <v>10.001990068486075</v>
       </c>
-      <c r="AH33" s="95" t="s">
+      <c r="AH33" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="AI33" s="95"/>
-      <c r="AJ33" s="95"/>
+      <c r="AI33" s="97"/>
+      <c r="AJ33" s="97"/>
     </row>
     <row r="34" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B34" s="12" t="s">
@@ -7538,9 +7538,9 @@
       </c>
       <c r="Y34" s="6"/>
       <c r="Z34" s="24"/>
-      <c r="AA34" s="95"/>
-      <c r="AB34" s="95"/>
-      <c r="AC34" s="95"/>
+      <c r="AA34" s="97"/>
+      <c r="AB34" s="97"/>
+      <c r="AC34" s="97"/>
       <c r="AD34" t="s">
         <v>80</v>
       </c>
@@ -7548,11 +7548,11 @@
         <f>(AF20*(1.02)^20)/AF20</f>
         <v>1.4859473959783542</v>
       </c>
-      <c r="AH34" s="95" t="s">
+      <c r="AH34" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="AI34" s="95"/>
-      <c r="AJ34" s="95"/>
+      <c r="AI34" s="97"/>
+      <c r="AJ34" s="97"/>
     </row>
     <row r="35" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B35" s="14" t="s">
@@ -7592,9 +7592,9 @@
         <v>4.1426409411833536</v>
       </c>
       <c r="Z35" s="6"/>
-      <c r="AA35" s="95"/>
-      <c r="AB35" s="95"/>
-      <c r="AC35" s="95"/>
+      <c r="AA35" s="97"/>
+      <c r="AB35" s="97"/>
+      <c r="AC35" s="97"/>
       <c r="AD35" t="s">
         <v>105</v>
       </c>
@@ -7672,17 +7672,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="AK4:AZ4"/>
-    <mergeCell ref="AM19:AZ19"/>
-    <mergeCell ref="AM5:AZ5"/>
-    <mergeCell ref="AH20:AJ20"/>
-    <mergeCell ref="AH25:AJ25"/>
-    <mergeCell ref="AK7:AK15"/>
-    <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="AA10:AC10"/>
-    <mergeCell ref="AH33:AJ33"/>
-    <mergeCell ref="AH32:AJ32"/>
-    <mergeCell ref="AK20:AK31"/>
     <mergeCell ref="AA34:AC34"/>
     <mergeCell ref="AH34:AJ34"/>
     <mergeCell ref="AA35:AC35"/>
@@ -7699,6 +7688,17 @@
     <mergeCell ref="AA31:AC31"/>
     <mergeCell ref="AA8:AC8"/>
     <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AA5:AC5"/>
+    <mergeCell ref="AA10:AC10"/>
+    <mergeCell ref="AH33:AJ33"/>
+    <mergeCell ref="AH32:AJ32"/>
+    <mergeCell ref="AK20:AK31"/>
+    <mergeCell ref="AK4:AZ4"/>
+    <mergeCell ref="AM19:AZ19"/>
+    <mergeCell ref="AM5:AZ5"/>
+    <mergeCell ref="AH20:AJ20"/>
+    <mergeCell ref="AH25:AJ25"/>
+    <mergeCell ref="AK7:AK15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7867,11 +7867,11 @@
       <c r="Z4" s="2">
         <v>2047</v>
       </c>
-      <c r="AA4" s="93" t="s">
+      <c r="AA4" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="AB4" s="93"/>
-      <c r="AC4" s="93"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="98"/>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -9213,7 +9213,7 @@
       <c r="G4" s="5">
         <v>1.06</v>
       </c>
-      <c r="H4" s="98">
+      <c r="H4" s="93">
         <v>-0.52</v>
       </c>
       <c r="I4" s="5">
@@ -9223,7 +9223,7 @@
       <c r="J4" s="5">
         <v>36.700000000000003</v>
       </c>
-      <c r="K4" s="99">
+      <c r="K4" s="94">
         <f>J4/I4</f>
         <v>28.230769230769234</v>
       </c>
@@ -9235,16 +9235,16 @@
       <c r="E5">
         <v>16.440000000000001</v>
       </c>
-      <c r="F5" s="100">
+      <c r="F5" s="95">
         <v>11.09</v>
       </c>
-      <c r="G5" s="100">
+      <c r="G5" s="95">
         <v>-41.84</v>
       </c>
-      <c r="H5" s="100">
+      <c r="H5" s="95">
         <v>-53.17</v>
       </c>
-      <c r="I5" s="100">
+      <c r="I5" s="95">
         <f>SUM(E5:H5)</f>
         <v>-67.48</v>
       </c>
@@ -9259,7 +9259,7 @@
       <c r="F6" s="5">
         <v>0.17</v>
       </c>
-      <c r="G6" s="98">
+      <c r="G6" s="93">
         <v>-0.11</v>
       </c>
       <c r="H6" s="5">
@@ -9272,7 +9272,7 @@
       <c r="J6" s="5">
         <v>36.700000000000003</v>
       </c>
-      <c r="K6" s="99">
+      <c r="K6" s="94">
         <f>J6/I6</f>
         <v>215.88235294117646</v>
       </c>
@@ -9281,26 +9281,26 @@
       <c r="B7" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="98">
+      <c r="E7" s="93">
         <v>-2.25</v>
       </c>
       <c r="F7" s="30">
         <v>0.32</v>
       </c>
-      <c r="G7" s="98">
+      <c r="G7" s="93">
         <v>-0.38</v>
       </c>
-      <c r="H7" s="98">
+      <c r="H7" s="93">
         <v>-1.24</v>
       </c>
-      <c r="I7" s="98">
+      <c r="I7" s="93">
         <f>SUM(E7:H7)</f>
         <v>-3.55</v>
       </c>
       <c r="J7" s="5">
         <v>36.700000000000003</v>
       </c>
-      <c r="K7" s="100">
+      <c r="K7" s="95">
         <f>J7/I7</f>
         <v>-10.338028169014086</v>
       </c>
@@ -9309,7 +9309,7 @@
       <c r="B8" t="s">
         <v>121</v>
       </c>
-      <c r="E8" s="100">
+      <c r="E8" s="95">
         <v>-48.2</v>
       </c>
       <c r="F8" s="5">
@@ -9321,7 +9321,7 @@
       <c r="H8" s="5">
         <v>217.92</v>
       </c>
-      <c r="I8" s="100">
+      <c r="I8" s="95">
         <f>SUM(E8:H8)</f>
         <v>328.01</v>
       </c>
